--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/basellm/models/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88A1329-C39F-BD4D-AA88-1DF651C5903E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D293F0D8-252D-3448-A595-69F0259362A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21300" yWindow="2100" windowWidth="28800" windowHeight="19480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22420" yWindow="14640" windowWidth="28800" windowHeight="19480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="96">
   <si>
     <t>name</t>
   </si>
@@ -255,9 +255,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>icon_url</t>
-  </si>
-  <si>
     <t>providerid</t>
   </si>
   <si>
@@ -279,14 +276,6 @@
   </si>
   <si>
     <t>model</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>baseurl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>api网址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -310,10 +299,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>图标URL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>说明</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -323,6 +308,42 @@
   </si>
   <si>
     <t>名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upappid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上位系统id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apiname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接口名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>providerid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ownerid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属机构id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -751,10 +772,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>77</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
@@ -780,7 +801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -835,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>10</v>
@@ -846,10 +867,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>10</v>
@@ -863,7 +884,7 @@
         <v>71</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>10</v>
@@ -874,24 +895,24 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D6">
-        <v>500</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>10</v>
@@ -902,45 +923,67 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="8" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="8" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="8" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="C11" s="8"/>
+      <c r="A11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="C12" s="8"/>
+      <c r="A12" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="C13" s="8"/>
@@ -956,6 +999,12 @@
     </row>
     <row r="17" spans="3:3">
       <c r="C17" s="8"/>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -968,13 +1017,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C18:C320</xm:sqref>
+          <xm:sqref>C20:C322</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0DC840C-C4F4-E845-8271-FD5C5D5F6FC3}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C17</xm:sqref>
+          <xm:sqref>C2:C19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1067,16 +1116,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>66</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1208,7 +1257,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D293F0D8-252D-3448-A595-69F0259362A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBCB6FF-17B3-6047-8274-68C977F4FA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22420" yWindow="14640" windowWidth="28800" windowHeight="19480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22420" yWindow="14640" windowWidth="28800" windowHeight="19480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="100">
   <si>
     <t>name</t>
   </si>
@@ -345,6 +345,22 @@
   <si>
     <t>所属机构id</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iconid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>svgicon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1094,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D73A0C9-9802-0C4C-A2B3-372B9ED806BE}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1126,6 +1142,20 @@
       </c>
       <c r="D2" s="8" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBCB6FF-17B3-6047-8274-68C977F4FA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301FD715-9ABA-B04F-AA77-6F3E8E728495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22420" yWindow="14640" windowWidth="28800" windowHeight="19480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="111">
   <si>
     <t>name</t>
   </si>
@@ -360,6 +360,49 @@
   </si>
   <si>
     <t>icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>llmcatelogid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模型类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>llmcatelogid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>llmcatelog</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>upappid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>upapp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ownerid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>organization</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>orgname</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -817,7 +860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -903,7 +946,7 @@
         <v>84</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="D5">
         <v>500</v>
@@ -911,10 +954,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>10</v>
@@ -925,52 +968,52 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D7">
-        <v>500</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D9">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>10</v>
@@ -981,28 +1024,39 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="C13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="C14" s="8"/>
@@ -1021,6 +1075,9 @@
     </row>
     <row r="19" spans="3:3">
       <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1033,13 +1090,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C20:C322</xm:sqref>
+          <xm:sqref>C21:C323</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0DC840C-C4F4-E845-8271-FD5C5D5F6FC3}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C19</xm:sqref>
+          <xm:sqref>C2:C20</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1110,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D73A0C9-9802-0C4C-A2B3-372B9ED806BE}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1156,6 +1213,48 @@
       </c>
       <c r="D3" s="7" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301FD715-9ABA-B04F-AA77-6F3E8E728495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EFE9B0-B20B-0049-8437-947C97B1A913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22420" yWindow="14640" windowWidth="28800" windowHeight="19480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="14500" windowHeight="23400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="110">
   <si>
     <t>name</t>
   </si>
@@ -356,10 +356,6 @@
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -946,7 +942,7 @@
         <v>84</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5">
         <v>500</v>
@@ -954,10 +950,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>10</v>
@@ -1212,49 +1208,49 @@
         <v>98</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>104</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>98</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>107</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>98</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>109</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>98</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EFE9B0-B20B-0049-8437-947C97B1A913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE8DDED-B2B4-E742-841F-D49EEB14B457}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="14500" windowHeight="23400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -21,23 +21,11 @@
     <sheet name="help" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="113">
   <si>
     <t>name</t>
   </si>
@@ -400,6 +388,18 @@
   <si>
     <t>orgname</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果查询接口名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>str</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query_apiname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -856,7 +856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -1055,7 +1055,18 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="C14" s="8"/>
+      <c r="A14" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="C15" s="8"/>
@@ -1074,6 +1085,9 @@
     </row>
     <row r="20" spans="3:3">
       <c r="C20" s="8"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1086,13 +1100,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C21:C323</xm:sqref>
+          <xm:sqref>C22:C324</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0DC840C-C4F4-E845-8271-FD5C5D5F6FC3}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C20</xm:sqref>
+          <xm:sqref>C2:C9 C10:C21</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE8DDED-B2B4-E742-841F-D49EEB14B457}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943E761C-BC43-B144-BB3F-AED1ABFE439D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="116">
   <si>
     <t>name</t>
   </si>
@@ -399,6 +399,18 @@
   </si>
   <si>
     <t>query_apiname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query_period</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询间隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1069,7 +1081,15 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="C15" s="8"/>
+      <c r="A15" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="C16" s="8"/>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943E761C-BC43-B144-BB3F-AED1ABFE439D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B0161B-97D3-364D-AD80-1ECE74C4341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="19600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,10 +267,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enable_date</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>启用日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -411,6 +407,10 @@
   </si>
   <si>
     <t>long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enabled_date</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>10</v>
@@ -937,7 +937,7 @@
         <v>78</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>10</v>
@@ -951,10 +951,10 @@
         <v>71</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>500</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>10</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>10</v>
@@ -1004,10 +1004,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>10</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>73</v>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>95</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>10</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>32</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>32</v>
@@ -1068,13 +1068,13 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -1082,13 +1082,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1233,58 +1233,58 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>98</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C4" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="C5" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B0161B-97D3-364D-AD80-1ECE74C4341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F9C1F9-FE34-EB49-B206-870739FDACF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="126040" yWindow="7160" windowWidth="19600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="119">
   <si>
     <t>name</t>
   </si>
@@ -411,6 +411,18 @@
   </si>
   <si>
     <t>enabled_date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pricingmode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计费模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yes</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1090,9 +1102,26 @@
       <c r="C15" s="8" t="s">
         <v>114</v>
       </c>
+      <c r="G15">
+        <v>30</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="C16" s="8"/>
+      <c r="A16" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" s="8"/>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F9C1F9-FE34-EB49-B206-870739FDACF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF181962-616F-1E4D-9BFC-1E97ED3F523D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="126040" yWindow="7160" windowWidth="19600" windowHeight="18800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="58500" yWindow="12760" windowWidth="40960" windowHeight="23460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -414,15 +414,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>pricingmode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>计费模式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>yes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ppid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计费项目id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1108,19 +1108,19 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="3:3">

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF181962-616F-1E4D-9BFC-1E97ED3F523D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CA1143-E2B7-F94C-9D33-DF1A17777690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58500" yWindow="12760" windowWidth="40960" windowHeight="23460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="58500" yWindow="12760" windowWidth="40960" windowHeight="23460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="120">
   <si>
     <t>name</t>
   </si>
@@ -424,6 +424,10 @@
   <si>
     <t>计费项目id</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ppid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1226,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D73A0C9-9802-0C4C-A2B3-372B9ED806BE}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1314,6 +1318,17 @@
       </c>
       <c r="D6" s="7" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9CA1143-E2B7-F94C-9D33-DF1A17777690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73C07F1-9450-BC49-B6CB-AFF918FC644E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="58500" yWindow="12760" windowWidth="40960" windowHeight="23460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="121">
   <si>
     <t>name</t>
   </si>
@@ -427,6 +427,10 @@
   </si>
   <si>
     <t>ppid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pricing_program</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1232,6 +1236,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D73A0C9-9802-0C4C-A2B3-372B9ED806BE}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="8" t="s">
@@ -1321,8 +1328,11 @@
       </c>
     </row>
     <row r="7" spans="1:5">
+      <c r="A7" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="B7" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>97</v>

--- a/models/llm.xlsx
+++ b/models/llm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/llmage/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73C07F1-9450-BC49-B6CB-AFF918FC644E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B3EFA2-91B4-AB46-99A5-94E75E8F70DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58500" yWindow="12760" windowWidth="40960" windowHeight="23460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="58500" yWindow="12760" windowWidth="40960" windowHeight="23460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="124">
   <si>
     <t>name</t>
   </si>
@@ -432,6 +432,18 @@
   <si>
     <t>pricing_program</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>min_balance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最低余额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1131,19 +1143,36 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="3:3">
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="3:3">
+    <row r="17" spans="1:7">
+      <c r="A17" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="C18" s="8"/>
     </row>
-    <row r="19" spans="3:3">
+    <row r="19" spans="1:7">
       <c r="C19" s="8"/>
     </row>
-    <row r="20" spans="3:3">
+    <row r="20" spans="1:7">
       <c r="C20" s="8"/>
     </row>
-    <row r="21" spans="3:3">
+    <row r="21" spans="1:7">
       <c r="C21" s="8"/>
     </row>
   </sheetData>
